--- a/docs/tables/frame_count_study_summary.xlsx
+++ b/docs/tables/frame_count_study_summary.xlsx
@@ -594,22 +594,22 @@
         <v>27.08</v>
       </c>
       <c r="N2" t="n">
-        <v>34.85</v>
+        <v>35.36</v>
       </c>
       <c r="O2" t="n">
-        <v>47.76</v>
+        <v>47.64</v>
       </c>
       <c r="P2" t="n">
-        <v>83.31999999999999</v>
+        <v>83.22</v>
       </c>
       <c r="Q2" t="n">
-        <v>92.55</v>
+        <v>92.56999999999999</v>
       </c>
       <c r="R2" t="n">
-        <v>21.78</v>
+        <v>22.12</v>
       </c>
       <c r="S2" t="n">
-        <v>32.81</v>
+        <v>32.56</v>
       </c>
       <c r="T2" t="n">
         <v>1.33</v>
@@ -662,22 +662,22 @@
         <v>71.22</v>
       </c>
       <c r="N3" t="n">
-        <v>76.68000000000001</v>
+        <v>76.38</v>
       </c>
       <c r="O3" t="n">
-        <v>83.22</v>
+        <v>83.25</v>
       </c>
       <c r="P3" t="n">
-        <v>87.86</v>
+        <v>87.8</v>
       </c>
       <c r="Q3" t="n">
-        <v>94.41</v>
+        <v>94.45</v>
       </c>
       <c r="R3" t="n">
-        <v>66.45</v>
+        <v>66.04000000000001</v>
       </c>
       <c r="S3" t="n">
-        <v>75.97</v>
+        <v>75.76000000000001</v>
       </c>
       <c r="T3" t="n">
         <v>1.214</v>
@@ -730,22 +730,22 @@
         <v>77.51000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>80.48</v>
+        <v>80.5</v>
       </c>
       <c r="O4" t="n">
-        <v>85.68000000000001</v>
+        <v>85.76000000000001</v>
       </c>
       <c r="P4" t="n">
-        <v>86.40000000000001</v>
+        <v>86.48</v>
       </c>
       <c r="Q4" t="n">
-        <v>92.73999999999999</v>
+        <v>92.81</v>
       </c>
       <c r="R4" t="n">
-        <v>73.52</v>
+        <v>73.65000000000001</v>
       </c>
       <c r="S4" t="n">
-        <v>81.31</v>
+        <v>81.27</v>
       </c>
       <c r="T4" t="n">
         <v>1.311</v>
@@ -798,22 +798,22 @@
         <v>85.23</v>
       </c>
       <c r="N5" t="n">
-        <v>86.95</v>
+        <v>87</v>
       </c>
       <c r="O5" t="n">
-        <v>90.64</v>
+        <v>90.75</v>
       </c>
       <c r="P5" t="n">
-        <v>90.54000000000001</v>
+        <v>90.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>95.11</v>
+        <v>95.14</v>
       </c>
       <c r="R5" t="n">
-        <v>82.29000000000001</v>
+        <v>82.28</v>
       </c>
       <c r="S5" t="n">
-        <v>87.86</v>
+        <v>87.95999999999999</v>
       </c>
       <c r="T5" t="n">
         <v>1.335</v>
@@ -866,22 +866,22 @@
         <v>96.56</v>
       </c>
       <c r="N6" t="n">
-        <v>91.95999999999999</v>
+        <v>92</v>
       </c>
       <c r="O6" t="n">
-        <v>94.7</v>
+        <v>94.73</v>
       </c>
       <c r="P6" t="n">
-        <v>88</v>
+        <v>88.03</v>
       </c>
       <c r="Q6" t="n">
-        <v>92.69</v>
+        <v>92.70999999999999</v>
       </c>
       <c r="R6" t="n">
-        <v>95.13</v>
+        <v>95.20999999999999</v>
       </c>
       <c r="S6" t="n">
-        <v>97.66</v>
+        <v>97.73999999999999</v>
       </c>
       <c r="T6" t="n">
         <v>1.198</v>
@@ -934,22 +934,22 @@
         <v>97.06999999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>92.42</v>
+        <v>92.48</v>
       </c>
       <c r="O7" t="n">
-        <v>94.97</v>
+        <v>95.05</v>
       </c>
       <c r="P7" t="n">
-        <v>88.45</v>
+        <v>88.42</v>
       </c>
       <c r="Q7" t="n">
-        <v>92.84999999999999</v>
+        <v>92.94</v>
       </c>
       <c r="R7" t="n">
-        <v>95.95999999999999</v>
+        <v>95.97</v>
       </c>
       <c r="S7" t="n">
-        <v>98.02</v>
+        <v>98.01000000000001</v>
       </c>
       <c r="T7" t="n">
         <v>1.22</v>
@@ -1002,22 +1002,22 @@
         <v>97.66</v>
       </c>
       <c r="N8" t="n">
-        <v>92.8</v>
+        <v>92.69</v>
       </c>
       <c r="O8" t="n">
-        <v>95.47</v>
+        <v>95.37</v>
       </c>
       <c r="P8" t="n">
         <v>88.41</v>
       </c>
       <c r="Q8" t="n">
-        <v>93.18000000000001</v>
+        <v>93.05</v>
       </c>
       <c r="R8" t="n">
-        <v>96.69</v>
+        <v>96.66</v>
       </c>
       <c r="S8" t="n">
-        <v>98.51000000000001</v>
+        <v>98.48999999999999</v>
       </c>
       <c r="T8" t="n">
         <v>1.233</v>
@@ -1070,22 +1070,22 @@
         <v>96.31999999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>92.01000000000001</v>
+        <v>92.03</v>
       </c>
       <c r="O9" t="n">
-        <v>94.65000000000001</v>
+        <v>94.56</v>
       </c>
       <c r="P9" t="n">
-        <v>88.36</v>
+        <v>88.25</v>
       </c>
       <c r="Q9" t="n">
-        <v>92.77</v>
+        <v>92.67</v>
       </c>
       <c r="R9" t="n">
-        <v>95.04000000000001</v>
+        <v>95.06</v>
       </c>
       <c r="S9" t="n">
-        <v>97.42</v>
+        <v>97.34999999999999</v>
       </c>
       <c r="T9" t="n">
         <v>1.268</v>
@@ -1123,43 +1123,43 @@
         <v>0.25</v>
       </c>
       <c r="I10" t="n">
-        <v>2.202</v>
+        <v>1.752</v>
       </c>
       <c r="J10" t="n">
         <v>1.546</v>
       </c>
       <c r="K10" t="n">
-        <v>65.92</v>
+        <v>73.87</v>
       </c>
       <c r="L10" t="n">
-        <v>59.68</v>
+        <v>74.14</v>
       </c>
       <c r="M10" t="n">
         <v>73.59999999999999</v>
       </c>
       <c r="N10" t="n">
-        <v>63.43</v>
+        <v>71.59</v>
       </c>
       <c r="O10" t="n">
-        <v>68.45999999999999</v>
+        <v>76.03</v>
       </c>
       <c r="P10" t="n">
-        <v>56.26</v>
+        <v>71.18000000000001</v>
       </c>
       <c r="Q10" t="n">
-        <v>63.18</v>
+        <v>76.95999999999999</v>
       </c>
       <c r="R10" t="n">
-        <v>70.11</v>
+        <v>70.18000000000001</v>
       </c>
       <c r="S10" t="n">
-        <v>76.90000000000001</v>
+        <v>76.81</v>
       </c>
       <c r="T10" t="n">
         <v>1.631</v>
       </c>
       <c r="U10" t="n">
-        <v>11971</v>
+        <v>14583</v>
       </c>
     </row>
     <row r="11">
@@ -1191,43 +1191,43 @@
         <v>0.5</v>
       </c>
       <c r="I11" t="n">
-        <v>1.726</v>
+        <v>1.454</v>
       </c>
       <c r="J11" t="n">
         <v>0.751</v>
       </c>
       <c r="K11" t="n">
-        <v>77.42</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="L11" t="n">
-        <v>67.73999999999999</v>
+        <v>80.08</v>
       </c>
       <c r="M11" t="n">
         <v>90.33</v>
       </c>
       <c r="N11" t="n">
-        <v>75.5</v>
+        <v>83.3</v>
       </c>
       <c r="O11" t="n">
-        <v>79.47</v>
+        <v>86.45999999999999</v>
       </c>
       <c r="P11" t="n">
-        <v>64.95</v>
+        <v>77.86</v>
       </c>
       <c r="Q11" t="n">
-        <v>70.56</v>
+        <v>82.05</v>
       </c>
       <c r="R11" t="n">
-        <v>88.03</v>
+        <v>88.17</v>
       </c>
       <c r="S11" t="n">
-        <v>92.48999999999999</v>
+        <v>92.54000000000001</v>
       </c>
       <c r="T11" t="n">
         <v>1.5</v>
       </c>
       <c r="U11" t="n">
-        <v>14404</v>
+        <v>17799</v>
       </c>
     </row>
     <row r="12">
@@ -1259,43 +1259,43 @@
         <v>0.75</v>
       </c>
       <c r="I12" t="n">
-        <v>1.644</v>
+        <v>1.378</v>
       </c>
       <c r="J12" t="n">
         <v>0.577</v>
       </c>
       <c r="K12" t="n">
-        <v>77.65000000000001</v>
+        <v>85.28</v>
       </c>
       <c r="L12" t="n">
-        <v>68.62</v>
+        <v>81.51000000000001</v>
       </c>
       <c r="M12" t="n">
         <v>89.42</v>
       </c>
       <c r="N12" t="n">
-        <v>75.59</v>
+        <v>83.66</v>
       </c>
       <c r="O12" t="n">
-        <v>79.72</v>
+        <v>86.81</v>
       </c>
       <c r="P12" t="n">
-        <v>65.77</v>
+        <v>79.38</v>
       </c>
       <c r="Q12" t="n">
-        <v>71.45999999999999</v>
+        <v>83.51000000000001</v>
       </c>
       <c r="R12" t="n">
-        <v>87.05</v>
+        <v>86.93000000000001</v>
       </c>
       <c r="S12" t="n">
-        <v>91.70999999999999</v>
+        <v>91.73999999999999</v>
       </c>
       <c r="T12" t="n">
         <v>1.482</v>
       </c>
       <c r="U12" t="n">
-        <v>15053</v>
+        <v>18482</v>
       </c>
     </row>
     <row r="13">
@@ -1327,43 +1327,43 @@
         <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>1.673</v>
+        <v>1.4</v>
       </c>
       <c r="J13" t="n">
         <v>0.755</v>
       </c>
       <c r="K13" t="n">
-        <v>77.26000000000001</v>
+        <v>85.95999999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>67.86</v>
+        <v>82.53</v>
       </c>
       <c r="M13" t="n">
         <v>89.68000000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>75.06</v>
+        <v>84.42</v>
       </c>
       <c r="O13" t="n">
-        <v>79.34</v>
+        <v>87.54000000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>64.84999999999999</v>
+        <v>80.45</v>
       </c>
       <c r="Q13" t="n">
-        <v>70.93000000000001</v>
+        <v>84.58</v>
       </c>
       <c r="R13" t="n">
-        <v>87.22</v>
+        <v>87.34</v>
       </c>
       <c r="S13" t="n">
-        <v>91.81999999999999</v>
+        <v>92.03</v>
       </c>
       <c r="T13" t="n">
         <v>1.495</v>
       </c>
       <c r="U13" t="n">
-        <v>15051</v>
+        <v>18934</v>
       </c>
     </row>
     <row r="14">
@@ -1395,43 +1395,43 @@
         <v>0.25</v>
       </c>
       <c r="I14" t="n">
-        <v>2.404</v>
+        <v>2.165</v>
       </c>
       <c r="J14" t="n">
         <v>0.9360000000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>76.18000000000001</v>
+        <v>83.45</v>
       </c>
       <c r="L14" t="n">
-        <v>63.57</v>
+        <v>74.37</v>
       </c>
       <c r="M14" t="n">
         <v>95.06</v>
       </c>
       <c r="N14" t="n">
-        <v>74.34</v>
+        <v>82.08</v>
       </c>
       <c r="O14" t="n">
-        <v>78</v>
+        <v>84.77</v>
       </c>
       <c r="P14" t="n">
-        <v>61.12</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="Q14" t="n">
-        <v>65.98999999999999</v>
+        <v>76.31</v>
       </c>
       <c r="R14" t="n">
-        <v>93.56999999999999</v>
+        <v>93.55</v>
       </c>
       <c r="S14" t="n">
-        <v>96.45999999999999</v>
+        <v>96.43000000000001</v>
       </c>
       <c r="T14" t="n">
         <v>1.914</v>
       </c>
       <c r="U14" t="n">
-        <v>35569</v>
+        <v>40947</v>
       </c>
     </row>
     <row r="15">
@@ -1463,34 +1463,34 @@
         <v>0.5</v>
       </c>
       <c r="I15" t="n">
-        <v>2.298</v>
+        <v>1.896</v>
       </c>
       <c r="J15" t="n">
         <v>0.825</v>
       </c>
       <c r="K15" t="n">
-        <v>75.23</v>
+        <v>84.23</v>
       </c>
       <c r="L15" t="n">
-        <v>60.45</v>
+        <v>72.98</v>
       </c>
       <c r="M15" t="n">
         <v>99.56999999999999</v>
       </c>
       <c r="N15" t="n">
-        <v>73.18000000000001</v>
+        <v>82.76000000000001</v>
       </c>
       <c r="O15" t="n">
-        <v>77.14</v>
+        <v>85.64</v>
       </c>
       <c r="P15" t="n">
-        <v>57.83</v>
+        <v>70.78</v>
       </c>
       <c r="Q15" t="n">
-        <v>62.99</v>
+        <v>75.18000000000001</v>
       </c>
       <c r="R15" t="n">
-        <v>99.26000000000001</v>
+        <v>99.23999999999999</v>
       </c>
       <c r="S15" t="n">
         <v>99.83</v>
@@ -1499,7 +1499,7 @@
         <v>1.726</v>
       </c>
       <c r="U15" t="n">
-        <v>28422</v>
+        <v>34804</v>
       </c>
     </row>
     <row r="16">
@@ -1531,34 +1531,34 @@
         <v>0.75</v>
       </c>
       <c r="I16" t="n">
-        <v>2.412</v>
+        <v>1.879</v>
       </c>
       <c r="J16" t="n">
         <v>0.792</v>
       </c>
       <c r="K16" t="n">
-        <v>73.15000000000001</v>
+        <v>85.92</v>
       </c>
       <c r="L16" t="n">
-        <v>57.8</v>
+        <v>75.54000000000001</v>
       </c>
       <c r="M16" t="n">
         <v>99.61</v>
       </c>
       <c r="N16" t="n">
-        <v>71.14</v>
+        <v>84.62</v>
       </c>
       <c r="O16" t="n">
-        <v>75.08</v>
+        <v>87.20999999999999</v>
       </c>
       <c r="P16" t="n">
-        <v>55.34</v>
+        <v>73.56</v>
       </c>
       <c r="Q16" t="n">
-        <v>60.24</v>
+        <v>77.53</v>
       </c>
       <c r="R16" t="n">
-        <v>99.34999999999999</v>
+        <v>99.33</v>
       </c>
       <c r="S16" t="n">
         <v>99.83</v>
@@ -1567,7 +1567,7 @@
         <v>1.748</v>
       </c>
       <c r="U16" t="n">
-        <v>30871</v>
+        <v>41704</v>
       </c>
     </row>
     <row r="17">
@@ -1599,43 +1599,43 @@
         <v>1</v>
       </c>
       <c r="I17" t="n">
-        <v>2.536</v>
+        <v>1.976</v>
       </c>
       <c r="J17" t="n">
         <v>0.661</v>
       </c>
       <c r="K17" t="n">
-        <v>71.81</v>
+        <v>84.03</v>
       </c>
       <c r="L17" t="n">
-        <v>56.11</v>
+        <v>72.62</v>
       </c>
       <c r="M17" t="n">
         <v>99.7</v>
       </c>
       <c r="N17" t="n">
-        <v>69.81999999999999</v>
+        <v>82.79000000000001</v>
       </c>
       <c r="O17" t="n">
-        <v>73.59</v>
+        <v>85.3</v>
       </c>
       <c r="P17" t="n">
-        <v>53.72</v>
+        <v>70.79000000000001</v>
       </c>
       <c r="Q17" t="n">
-        <v>58.35</v>
+        <v>74.54000000000001</v>
       </c>
       <c r="R17" t="n">
-        <v>99.39</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="S17" t="n">
-        <v>99.92</v>
+        <v>99.95999999999999</v>
       </c>
       <c r="T17" t="n">
         <v>1.769</v>
       </c>
       <c r="U17" t="n">
-        <v>39644</v>
+        <v>51047</v>
       </c>
     </row>
     <row r="18">
@@ -1667,34 +1667,34 @@
         <v>0.25</v>
       </c>
       <c r="I18" t="n">
-        <v>2.155</v>
+        <v>1.871</v>
       </c>
       <c r="J18" t="n">
         <v>0.718</v>
       </c>
       <c r="K18" t="n">
-        <v>76.13</v>
+        <v>83.19</v>
       </c>
       <c r="L18" t="n">
-        <v>64.43000000000001</v>
+        <v>75.23999999999999</v>
       </c>
       <c r="M18" t="n">
         <v>93.04000000000001</v>
       </c>
       <c r="N18" t="n">
-        <v>74.2</v>
+        <v>81.69</v>
       </c>
       <c r="O18" t="n">
-        <v>78.04000000000001</v>
+        <v>84.47</v>
       </c>
       <c r="P18" t="n">
-        <v>61.76</v>
+        <v>72.97</v>
       </c>
       <c r="Q18" t="n">
-        <v>67.09999999999999</v>
+        <v>77.17</v>
       </c>
       <c r="R18" t="n">
-        <v>91.40000000000001</v>
+        <v>91.2</v>
       </c>
       <c r="S18" t="n">
         <v>94.66</v>
@@ -1703,7 +1703,7 @@
         <v>1.728</v>
       </c>
       <c r="U18" t="n">
-        <v>42993</v>
+        <v>48544</v>
       </c>
     </row>
     <row r="19">
@@ -1735,43 +1735,43 @@
         <v>0.5</v>
       </c>
       <c r="I19" t="n">
-        <v>2.506</v>
+        <v>2.216</v>
       </c>
       <c r="J19" t="n">
         <v>0.716</v>
       </c>
       <c r="K19" t="n">
-        <v>75.81999999999999</v>
+        <v>84.01000000000001</v>
       </c>
       <c r="L19" t="n">
-        <v>61.71</v>
+        <v>73.36</v>
       </c>
       <c r="M19" t="n">
         <v>98.28</v>
       </c>
       <c r="N19" t="n">
-        <v>74.15000000000001</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="O19" t="n">
-        <v>77.42</v>
+        <v>85.12</v>
       </c>
       <c r="P19" t="n">
-        <v>59.56</v>
+        <v>71.7</v>
       </c>
       <c r="Q19" t="n">
-        <v>63.82</v>
+        <v>75.06999999999999</v>
       </c>
       <c r="R19" t="n">
-        <v>97.48</v>
+        <v>97.44</v>
       </c>
       <c r="S19" t="n">
-        <v>98.98999999999999</v>
+        <v>98.95999999999999</v>
       </c>
       <c r="T19" t="n">
         <v>1.929</v>
       </c>
       <c r="U19" t="n">
-        <v>49893</v>
+        <v>57586</v>
       </c>
     </row>
     <row r="20">
@@ -1803,34 +1803,34 @@
         <v>0.75</v>
       </c>
       <c r="I20" t="n">
-        <v>1.878</v>
+        <v>1.61</v>
       </c>
       <c r="J20" t="n">
         <v>0.642</v>
       </c>
       <c r="K20" t="n">
-        <v>80.06999999999999</v>
+        <v>88.48</v>
       </c>
       <c r="L20" t="n">
-        <v>67.17</v>
+        <v>79.92</v>
       </c>
       <c r="M20" t="n">
         <v>99.09999999999999</v>
       </c>
       <c r="N20" t="n">
-        <v>78.25</v>
+        <v>87.27</v>
       </c>
       <c r="O20" t="n">
-        <v>81.75</v>
+        <v>89.62</v>
       </c>
       <c r="P20" t="n">
-        <v>64.63</v>
+        <v>78.01000000000001</v>
       </c>
       <c r="Q20" t="n">
-        <v>69.58</v>
+        <v>81.77</v>
       </c>
       <c r="R20" t="n">
-        <v>98.58</v>
+        <v>98.56999999999999</v>
       </c>
       <c r="S20" t="n">
         <v>99.53</v>
@@ -1839,7 +1839,7 @@
         <v>1.609</v>
       </c>
       <c r="U20" t="n">
-        <v>25986</v>
+        <v>33033</v>
       </c>
     </row>
     <row r="21">
@@ -1871,43 +1871,43 @@
         <v>1</v>
       </c>
       <c r="I21" t="n">
-        <v>2.187</v>
+        <v>1.706</v>
       </c>
       <c r="J21" t="n">
         <v>0.577</v>
       </c>
       <c r="K21" t="n">
-        <v>75.69</v>
+        <v>85.73999999999999</v>
       </c>
       <c r="L21" t="n">
-        <v>61.46</v>
+        <v>75.92</v>
       </c>
       <c r="M21" t="n">
         <v>98.5</v>
       </c>
       <c r="N21" t="n">
-        <v>73.73</v>
+        <v>84.41</v>
       </c>
       <c r="O21" t="n">
-        <v>77.59999999999999</v>
+        <v>87.04000000000001</v>
       </c>
       <c r="P21" t="n">
-        <v>58.91</v>
+        <v>73.87</v>
       </c>
       <c r="Q21" t="n">
-        <v>64.03</v>
+        <v>77.95</v>
       </c>
       <c r="R21" t="n">
         <v>97.83</v>
       </c>
       <c r="S21" t="n">
-        <v>99.11</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="T21" t="n">
         <v>1.644</v>
       </c>
       <c r="U21" t="n">
-        <v>24678</v>
+        <v>32773</v>
       </c>
     </row>
   </sheetData>

--- a/docs/tables/frame_count_study_summary.xlsx
+++ b/docs/tables/frame_count_study_summary.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="frame_count_study" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="significance" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,14 +28,28 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00585D54"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="000D8054"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F3864"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -49,9 +64,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,30 +436,36 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U21"/>
+  <dimension ref="A1:AA21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
     <col width="5" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
-    <col width="8" customWidth="1" min="11" max="11"/>
-    <col width="9" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="10" customWidth="1" min="15" max="15"/>
-    <col width="11" customWidth="1" min="16" max="16"/>
-    <col width="11" customWidth="1" min="17" max="17"/>
-    <col width="12" customWidth="1" min="18" max="18"/>
-    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="19" customWidth="1" min="17" max="17"/>
+    <col width="20" customWidth="1" min="18" max="18"/>
+    <col width="13" customWidth="1" min="19" max="19"/>
     <col width="17" customWidth="1" min="20" max="20"/>
-    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="15" customWidth="1" min="23" max="23"/>
+    <col width="15" customWidth="1" min="24" max="24"/>
+    <col width="16" customWidth="1" min="25" max="25"/>
+    <col width="16" customWidth="1" min="26" max="26"/>
+    <col width="17" customWidth="1" min="27" max="27"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -466,7 +491,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>reg_rate</t>
+          <t>reg-rate (%)</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -481,72 +506,102 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>N/N_max</t>
+          <t>accuracy median (cm)</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>accuracy_median_cm</t>
+          <t>completeness median (cm)</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>completeness_median_cm</t>
+          <t>inlier RMSE@3cm (mm)</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>F1@3cm</t>
+          <t>accuracy@3cm (%)</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Acc@3cm</t>
+          <t>completeness@3cm (%)</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Comp@3cm</t>
+          <t>F1@3cm (%)</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>F1_CI_lo</t>
+          <t>accuracy@5cm (%)</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>F1_CI_hi</t>
+          <t>completeness@5cm (%)</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Acc_CI_lo</t>
+          <t>F1@5cm (%)</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>Acc_CI_hi</t>
+          <t>accuracy@10cm (%)</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>Comp_CI_lo</t>
+          <t>completeness@10cm (%)</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>Comp_CI_hi</t>
+          <t>F1@10cm (%)</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>inlier_RMSE@3cm</t>
+          <t>ΔF1@10-3cm (pp)</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>n_excluded</t>
+          <t>F1@3cm CI lo</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>F1@3cm CI hi</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Acc@3cm CI lo</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Acc@3cm CI hi</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Comp@3cm CI lo</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Comp@3cm CI hi</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>excluded as gap</t>
         </is>
       </c>
     </row>
@@ -569,6 +624,9 @@
           <t>exp_115</t>
         </is>
       </c>
+      <c r="E2" t="n">
+        <v>100</v>
+      </c>
       <c r="F2" t="n">
         <v>11328</v>
       </c>
@@ -576,45 +634,63 @@
         <v>1458</v>
       </c>
       <c r="H2" t="n">
-        <v>0.25</v>
+        <v>1.143</v>
       </c>
       <c r="I2" t="n">
-        <v>1.143</v>
+        <v>6.495</v>
       </c>
       <c r="J2" t="n">
-        <v>6.495</v>
+        <v>13.3</v>
       </c>
       <c r="K2" t="n">
+        <v>88.47</v>
+      </c>
+      <c r="L2" t="n">
+        <v>27.08</v>
+      </c>
+      <c r="M2" t="n">
         <v>41.47</v>
       </c>
-      <c r="L2" t="n">
-        <v>88.47</v>
-      </c>
-      <c r="M2" t="n">
-        <v>27.08</v>
-      </c>
       <c r="N2" t="n">
+        <v>97.59</v>
+      </c>
+      <c r="O2" t="n">
+        <v>40.54</v>
+      </c>
+      <c r="P2" t="n">
+        <v>57.28</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>99.48</v>
+      </c>
+      <c r="R2" t="n">
+        <v>66.94</v>
+      </c>
+      <c r="S2" t="n">
+        <v>80.03</v>
+      </c>
+      <c r="T2" t="n">
+        <v>38.57</v>
+      </c>
+      <c r="U2" t="n">
         <v>35.36</v>
       </c>
-      <c r="O2" t="n">
+      <c r="V2" t="n">
         <v>47.64</v>
       </c>
-      <c r="P2" t="n">
+      <c r="W2" t="n">
         <v>83.22</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="X2" t="n">
         <v>92.56999999999999</v>
       </c>
-      <c r="R2" t="n">
+      <c r="Y2" t="n">
         <v>22.12</v>
       </c>
-      <c r="S2" t="n">
+      <c r="Z2" t="n">
         <v>32.56</v>
       </c>
-      <c r="T2" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="U2" t="n">
+      <c r="AA2" t="n">
         <v>296</v>
       </c>
     </row>
@@ -637,6 +713,9 @@
           <t>exp_116</t>
         </is>
       </c>
+      <c r="E3" t="n">
+        <v>100</v>
+      </c>
       <c r="F3" t="n">
         <v>54870</v>
       </c>
@@ -644,45 +723,63 @@
         <v>3608</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5</v>
+        <v>0.975</v>
       </c>
       <c r="I3" t="n">
-        <v>0.975</v>
+        <v>1.678</v>
       </c>
       <c r="J3" t="n">
-        <v>1.678</v>
+        <v>12.14</v>
       </c>
       <c r="K3" t="n">
+        <v>91.39</v>
+      </c>
+      <c r="L3" t="n">
+        <v>71.22</v>
+      </c>
+      <c r="M3" t="n">
         <v>80.05</v>
       </c>
-      <c r="L3" t="n">
-        <v>91.39</v>
-      </c>
-      <c r="M3" t="n">
-        <v>71.22</v>
-      </c>
       <c r="N3" t="n">
+        <v>99.19</v>
+      </c>
+      <c r="O3" t="n">
+        <v>92.68000000000001</v>
+      </c>
+      <c r="P3" t="n">
+        <v>95.81999999999999</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>99.83</v>
+      </c>
+      <c r="R3" t="n">
+        <v>100</v>
+      </c>
+      <c r="S3" t="n">
+        <v>99.92</v>
+      </c>
+      <c r="T3" t="n">
+        <v>19.86</v>
+      </c>
+      <c r="U3" t="n">
         <v>76.38</v>
       </c>
-      <c r="O3" t="n">
+      <c r="V3" t="n">
         <v>83.25</v>
       </c>
-      <c r="P3" t="n">
+      <c r="W3" t="n">
         <v>87.8</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="X3" t="n">
         <v>94.45</v>
       </c>
-      <c r="R3" t="n">
+      <c r="Y3" t="n">
         <v>66.04000000000001</v>
       </c>
-      <c r="S3" t="n">
+      <c r="Z3" t="n">
         <v>75.76000000000001</v>
       </c>
-      <c r="T3" t="n">
-        <v>1.214</v>
-      </c>
-      <c r="U3" t="n">
+      <c r="AA3" t="n">
         <v>658</v>
       </c>
     </row>
@@ -705,6 +802,9 @@
           <t>exp_117</t>
         </is>
       </c>
+      <c r="E4" t="n">
+        <v>100</v>
+      </c>
       <c r="F4" t="n">
         <v>124238</v>
       </c>
@@ -712,45 +812,63 @@
         <v>4940</v>
       </c>
       <c r="H4" t="n">
-        <v>0.75</v>
+        <v>1.102</v>
       </c>
       <c r="I4" t="n">
-        <v>1.102</v>
+        <v>1.523</v>
       </c>
       <c r="J4" t="n">
-        <v>1.523</v>
+        <v>13.11</v>
       </c>
       <c r="K4" t="n">
+        <v>89.8</v>
+      </c>
+      <c r="L4" t="n">
+        <v>77.51000000000001</v>
+      </c>
+      <c r="M4" t="n">
         <v>83.2</v>
       </c>
-      <c r="L4" t="n">
-        <v>89.8</v>
-      </c>
-      <c r="M4" t="n">
-        <v>77.51000000000001</v>
-      </c>
       <c r="N4" t="n">
+        <v>99.65000000000001</v>
+      </c>
+      <c r="O4" t="n">
+        <v>96.48</v>
+      </c>
+      <c r="P4" t="n">
+        <v>98.04000000000001</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>99.92</v>
+      </c>
+      <c r="R4" t="n">
+        <v>100</v>
+      </c>
+      <c r="S4" t="n">
+        <v>99.95999999999999</v>
+      </c>
+      <c r="T4" t="n">
+        <v>16.75</v>
+      </c>
+      <c r="U4" t="n">
         <v>80.5</v>
       </c>
-      <c r="O4" t="n">
+      <c r="V4" t="n">
         <v>85.76000000000001</v>
       </c>
-      <c r="P4" t="n">
+      <c r="W4" t="n">
         <v>86.48</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="X4" t="n">
         <v>92.81</v>
       </c>
-      <c r="R4" t="n">
+      <c r="Y4" t="n">
         <v>73.65000000000001</v>
       </c>
-      <c r="S4" t="n">
+      <c r="Z4" t="n">
         <v>81.27</v>
       </c>
-      <c r="T4" t="n">
-        <v>1.311</v>
-      </c>
-      <c r="U4" t="n">
+      <c r="AA4" t="n">
         <v>1245</v>
       </c>
     </row>
@@ -773,6 +891,9 @@
           <t>exp_118</t>
         </is>
       </c>
+      <c r="E5" t="n">
+        <v>100</v>
+      </c>
       <c r="F5" t="n">
         <v>163519</v>
       </c>
@@ -780,45 +901,63 @@
         <v>5396</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>1.171</v>
       </c>
       <c r="I5" t="n">
-        <v>1.171</v>
+        <v>1.336</v>
       </c>
       <c r="J5" t="n">
-        <v>1.336</v>
+        <v>13.35</v>
       </c>
       <c r="K5" t="n">
+        <v>92.95</v>
+      </c>
+      <c r="L5" t="n">
+        <v>85.23</v>
+      </c>
+      <c r="M5" t="n">
         <v>88.93000000000001</v>
       </c>
-      <c r="L5" t="n">
-        <v>92.95</v>
-      </c>
-      <c r="M5" t="n">
-        <v>85.23</v>
-      </c>
       <c r="N5" t="n">
+        <v>99.08</v>
+      </c>
+      <c r="O5" t="n">
+        <v>99.09</v>
+      </c>
+      <c r="P5" t="n">
+        <v>99.09</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>99.8</v>
+      </c>
+      <c r="R5" t="n">
+        <v>100</v>
+      </c>
+      <c r="S5" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="T5" t="n">
+        <v>10.97</v>
+      </c>
+      <c r="U5" t="n">
         <v>87</v>
       </c>
-      <c r="O5" t="n">
+      <c r="V5" t="n">
         <v>90.75</v>
       </c>
-      <c r="P5" t="n">
+      <c r="W5" t="n">
         <v>90.5</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="X5" t="n">
         <v>95.14</v>
       </c>
-      <c r="R5" t="n">
+      <c r="Y5" t="n">
         <v>82.28</v>
       </c>
-      <c r="S5" t="n">
+      <c r="Z5" t="n">
         <v>87.95999999999999</v>
       </c>
-      <c r="T5" t="n">
-        <v>1.335</v>
-      </c>
-      <c r="U5" t="n">
+      <c r="AA5" t="n">
         <v>927</v>
       </c>
     </row>
@@ -841,6 +980,9 @@
           <t>exp_119</t>
         </is>
       </c>
+      <c r="E6" t="n">
+        <v>100</v>
+      </c>
       <c r="F6" t="n">
         <v>230855</v>
       </c>
@@ -848,45 +990,63 @@
         <v>12009</v>
       </c>
       <c r="H6" t="n">
-        <v>0.25</v>
+        <v>0.995</v>
       </c>
       <c r="I6" t="n">
-        <v>0.995</v>
+        <v>0.493</v>
       </c>
       <c r="J6" t="n">
-        <v>0.493</v>
+        <v>11.98</v>
       </c>
       <c r="K6" t="n">
+        <v>90.42</v>
+      </c>
+      <c r="L6" t="n">
+        <v>96.56</v>
+      </c>
+      <c r="M6" t="n">
         <v>93.39</v>
       </c>
-      <c r="L6" t="n">
-        <v>90.42</v>
-      </c>
-      <c r="M6" t="n">
-        <v>96.56</v>
-      </c>
       <c r="N6" t="n">
+        <v>100</v>
+      </c>
+      <c r="O6" t="n">
+        <v>99.92</v>
+      </c>
+      <c r="P6" t="n">
+        <v>99.95999999999999</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>100</v>
+      </c>
+      <c r="R6" t="n">
+        <v>100</v>
+      </c>
+      <c r="S6" t="n">
+        <v>100</v>
+      </c>
+      <c r="T6" t="n">
+        <v>6.61</v>
+      </c>
+      <c r="U6" t="n">
         <v>92</v>
       </c>
-      <c r="O6" t="n">
+      <c r="V6" t="n">
         <v>94.73</v>
       </c>
-      <c r="P6" t="n">
+      <c r="W6" t="n">
         <v>88.03</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="X6" t="n">
         <v>92.70999999999999</v>
       </c>
-      <c r="R6" t="n">
+      <c r="Y6" t="n">
         <v>95.20999999999999</v>
       </c>
-      <c r="S6" t="n">
+      <c r="Z6" t="n">
         <v>97.73999999999999</v>
       </c>
-      <c r="T6" t="n">
-        <v>1.198</v>
-      </c>
-      <c r="U6" t="n">
+      <c r="AA6" t="n">
         <v>2773</v>
       </c>
     </row>
@@ -909,6 +1069,9 @@
           <t>exp_120</t>
         </is>
       </c>
+      <c r="E7" t="n">
+        <v>100</v>
+      </c>
       <c r="F7" t="n">
         <v>319227</v>
       </c>
@@ -916,45 +1079,63 @@
         <v>12464</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5</v>
+        <v>0.919</v>
       </c>
       <c r="I7" t="n">
-        <v>0.919</v>
+        <v>0.701</v>
       </c>
       <c r="J7" t="n">
-        <v>0.701</v>
+        <v>12.2</v>
       </c>
       <c r="K7" t="n">
+        <v>90.75</v>
+      </c>
+      <c r="L7" t="n">
+        <v>97.06999999999999</v>
+      </c>
+      <c r="M7" t="n">
         <v>93.8</v>
       </c>
-      <c r="L7" t="n">
-        <v>90.75</v>
-      </c>
-      <c r="M7" t="n">
-        <v>97.06999999999999</v>
-      </c>
       <c r="N7" t="n">
+        <v>99.97</v>
+      </c>
+      <c r="O7" t="n">
+        <v>100</v>
+      </c>
+      <c r="P7" t="n">
+        <v>99.98</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>99.97</v>
+      </c>
+      <c r="R7" t="n">
+        <v>100</v>
+      </c>
+      <c r="S7" t="n">
+        <v>99.98</v>
+      </c>
+      <c r="T7" t="n">
+        <v>6.18</v>
+      </c>
+      <c r="U7" t="n">
         <v>92.48</v>
       </c>
-      <c r="O7" t="n">
+      <c r="V7" t="n">
         <v>95.05</v>
       </c>
-      <c r="P7" t="n">
+      <c r="W7" t="n">
         <v>88.42</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="X7" t="n">
         <v>92.94</v>
       </c>
-      <c r="R7" t="n">
+      <c r="Y7" t="n">
         <v>95.97</v>
       </c>
-      <c r="S7" t="n">
+      <c r="Z7" t="n">
         <v>98.01000000000001</v>
       </c>
-      <c r="T7" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="U7" t="n">
+      <c r="AA7" t="n">
         <v>2847</v>
       </c>
     </row>
@@ -977,6 +1158,9 @@
           <t>exp_121</t>
         </is>
       </c>
+      <c r="E8" t="n">
+        <v>100</v>
+      </c>
       <c r="F8" t="n">
         <v>451687</v>
       </c>
@@ -984,45 +1168,63 @@
         <v>13032</v>
       </c>
       <c r="H8" t="n">
-        <v>0.75</v>
+        <v>0.997</v>
       </c>
       <c r="I8" t="n">
-        <v>0.997</v>
+        <v>0.66</v>
       </c>
       <c r="J8" t="n">
-        <v>0.66</v>
+        <v>12.33</v>
       </c>
       <c r="K8" t="n">
+        <v>90.84999999999999</v>
+      </c>
+      <c r="L8" t="n">
+        <v>97.66</v>
+      </c>
+      <c r="M8" t="n">
         <v>94.13</v>
       </c>
-      <c r="L8" t="n">
-        <v>90.84999999999999</v>
-      </c>
-      <c r="M8" t="n">
-        <v>97.66</v>
-      </c>
       <c r="N8" t="n">
+        <v>100</v>
+      </c>
+      <c r="O8" t="n">
+        <v>99.95999999999999</v>
+      </c>
+      <c r="P8" t="n">
+        <v>99.98</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>100</v>
+      </c>
+      <c r="R8" t="n">
+        <v>100</v>
+      </c>
+      <c r="S8" t="n">
+        <v>100</v>
+      </c>
+      <c r="T8" t="n">
+        <v>5.87</v>
+      </c>
+      <c r="U8" t="n">
         <v>92.69</v>
       </c>
-      <c r="O8" t="n">
+      <c r="V8" t="n">
         <v>95.37</v>
       </c>
-      <c r="P8" t="n">
+      <c r="W8" t="n">
         <v>88.41</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="X8" t="n">
         <v>93.05</v>
       </c>
-      <c r="R8" t="n">
+      <c r="Y8" t="n">
         <v>96.66</v>
       </c>
-      <c r="S8" t="n">
+      <c r="Z8" t="n">
         <v>98.48999999999999</v>
       </c>
-      <c r="T8" t="n">
-        <v>1.233</v>
-      </c>
-      <c r="U8" t="n">
+      <c r="AA8" t="n">
         <v>2899</v>
       </c>
     </row>
@@ -1045,6 +1247,9 @@
           <t>exp_122</t>
         </is>
       </c>
+      <c r="E9" t="n">
+        <v>100</v>
+      </c>
       <c r="F9" t="n">
         <v>481494</v>
       </c>
@@ -1052,45 +1257,63 @@
         <v>13643</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>0.988</v>
       </c>
       <c r="I9" t="n">
-        <v>0.988</v>
+        <v>0.678</v>
       </c>
       <c r="J9" t="n">
-        <v>0.678</v>
+        <v>12.68</v>
       </c>
       <c r="K9" t="n">
+        <v>90.62</v>
+      </c>
+      <c r="L9" t="n">
+        <v>96.31999999999999</v>
+      </c>
+      <c r="M9" t="n">
         <v>93.38</v>
       </c>
-      <c r="L9" t="n">
-        <v>90.62</v>
-      </c>
-      <c r="M9" t="n">
-        <v>96.31999999999999</v>
-      </c>
       <c r="N9" t="n">
+        <v>99.98</v>
+      </c>
+      <c r="O9" t="n">
+        <v>99.88</v>
+      </c>
+      <c r="P9" t="n">
+        <v>99.93000000000001</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>100</v>
+      </c>
+      <c r="R9" t="n">
+        <v>100</v>
+      </c>
+      <c r="S9" t="n">
+        <v>100</v>
+      </c>
+      <c r="T9" t="n">
+        <v>6.62</v>
+      </c>
+      <c r="U9" t="n">
         <v>92.03</v>
       </c>
-      <c r="O9" t="n">
+      <c r="V9" t="n">
         <v>94.56</v>
       </c>
-      <c r="P9" t="n">
+      <c r="W9" t="n">
         <v>88.25</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="X9" t="n">
         <v>92.67</v>
       </c>
-      <c r="R9" t="n">
+      <c r="Y9" t="n">
         <v>95.06</v>
       </c>
-      <c r="S9" t="n">
+      <c r="Z9" t="n">
         <v>97.34999999999999</v>
       </c>
-      <c r="T9" t="n">
-        <v>1.268</v>
-      </c>
-      <c r="U9" t="n">
+      <c r="AA9" t="n">
         <v>3013</v>
       </c>
     </row>
@@ -1113,6 +1336,9 @@
           <t>exp_109</t>
         </is>
       </c>
+      <c r="E10" t="n">
+        <v>100</v>
+      </c>
       <c r="F10" t="n">
         <v>327620</v>
       </c>
@@ -1120,45 +1346,63 @@
         <v>25370</v>
       </c>
       <c r="H10" t="n">
-        <v>0.25</v>
+        <v>1.752</v>
       </c>
       <c r="I10" t="n">
-        <v>1.752</v>
+        <v>1.546</v>
       </c>
       <c r="J10" t="n">
-        <v>1.546</v>
+        <v>16.31</v>
       </c>
       <c r="K10" t="n">
+        <v>74.14</v>
+      </c>
+      <c r="L10" t="n">
+        <v>73.59999999999999</v>
+      </c>
+      <c r="M10" t="n">
         <v>73.87</v>
       </c>
-      <c r="L10" t="n">
-        <v>74.14</v>
-      </c>
-      <c r="M10" t="n">
-        <v>73.59999999999999</v>
-      </c>
       <c r="N10" t="n">
+        <v>99.68000000000001</v>
+      </c>
+      <c r="O10" t="n">
+        <v>89.12</v>
+      </c>
+      <c r="P10" t="n">
+        <v>94.11</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="R10" t="n">
+        <v>96.81999999999999</v>
+      </c>
+      <c r="S10" t="n">
+        <v>98.33</v>
+      </c>
+      <c r="T10" t="n">
+        <v>24.47</v>
+      </c>
+      <c r="U10" t="n">
         <v>71.59</v>
       </c>
-      <c r="O10" t="n">
+      <c r="V10" t="n">
         <v>76.03</v>
       </c>
-      <c r="P10" t="n">
+      <c r="W10" t="n">
         <v>71.18000000000001</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="X10" t="n">
         <v>76.95999999999999</v>
       </c>
-      <c r="R10" t="n">
+      <c r="Y10" t="n">
         <v>70.18000000000001</v>
       </c>
-      <c r="S10" t="n">
+      <c r="Z10" t="n">
         <v>76.81</v>
       </c>
-      <c r="T10" t="n">
-        <v>1.631</v>
-      </c>
-      <c r="U10" t="n">
+      <c r="AA10" t="n">
         <v>14583</v>
       </c>
     </row>
@@ -1181,6 +1425,9 @@
           <t>exp_110</t>
         </is>
       </c>
+      <c r="E11" t="n">
+        <v>100</v>
+      </c>
       <c r="F11" t="n">
         <v>761844</v>
       </c>
@@ -1188,45 +1435,63 @@
         <v>36428</v>
       </c>
       <c r="H11" t="n">
-        <v>0.5</v>
+        <v>1.454</v>
       </c>
       <c r="I11" t="n">
-        <v>1.454</v>
+        <v>0.751</v>
       </c>
       <c r="J11" t="n">
-        <v>0.751</v>
+        <v>15</v>
       </c>
       <c r="K11" t="n">
+        <v>80.08</v>
+      </c>
+      <c r="L11" t="n">
+        <v>90.33</v>
+      </c>
+      <c r="M11" t="n">
         <v>84.90000000000001</v>
       </c>
-      <c r="L11" t="n">
-        <v>80.08</v>
-      </c>
-      <c r="M11" t="n">
-        <v>90.33</v>
-      </c>
       <c r="N11" t="n">
+        <v>99.68000000000001</v>
+      </c>
+      <c r="O11" t="n">
+        <v>95.61</v>
+      </c>
+      <c r="P11" t="n">
+        <v>97.61</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>99.91</v>
+      </c>
+      <c r="R11" t="n">
+        <v>99.73999999999999</v>
+      </c>
+      <c r="S11" t="n">
+        <v>99.83</v>
+      </c>
+      <c r="T11" t="n">
+        <v>14.93</v>
+      </c>
+      <c r="U11" t="n">
         <v>83.3</v>
       </c>
-      <c r="O11" t="n">
+      <c r="V11" t="n">
         <v>86.45999999999999</v>
       </c>
-      <c r="P11" t="n">
+      <c r="W11" t="n">
         <v>77.86</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="X11" t="n">
         <v>82.05</v>
       </c>
-      <c r="R11" t="n">
+      <c r="Y11" t="n">
         <v>88.17</v>
       </c>
-      <c r="S11" t="n">
+      <c r="Z11" t="n">
         <v>92.54000000000001</v>
       </c>
-      <c r="T11" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="U11" t="n">
+      <c r="AA11" t="n">
         <v>17799</v>
       </c>
     </row>
@@ -1249,6 +1514,9 @@
           <t>exp_111</t>
         </is>
       </c>
+      <c r="E12" t="n">
+        <v>100</v>
+      </c>
       <c r="F12" t="n">
         <v>1123433</v>
       </c>
@@ -1256,45 +1524,63 @@
         <v>36738</v>
       </c>
       <c r="H12" t="n">
-        <v>0.75</v>
+        <v>1.378</v>
       </c>
       <c r="I12" t="n">
-        <v>1.378</v>
+        <v>0.577</v>
       </c>
       <c r="J12" t="n">
-        <v>0.577</v>
+        <v>14.82</v>
       </c>
       <c r="K12" t="n">
+        <v>81.51000000000001</v>
+      </c>
+      <c r="L12" t="n">
+        <v>89.42</v>
+      </c>
+      <c r="M12" t="n">
         <v>85.28</v>
       </c>
-      <c r="L12" t="n">
-        <v>81.51000000000001</v>
-      </c>
-      <c r="M12" t="n">
-        <v>89.42</v>
-      </c>
       <c r="N12" t="n">
+        <v>99.68000000000001</v>
+      </c>
+      <c r="O12" t="n">
+        <v>95.23</v>
+      </c>
+      <c r="P12" t="n">
+        <v>97.40000000000001</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>99.87</v>
+      </c>
+      <c r="R12" t="n">
+        <v>99.7</v>
+      </c>
+      <c r="S12" t="n">
+        <v>99.79000000000001</v>
+      </c>
+      <c r="T12" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="U12" t="n">
         <v>83.66</v>
       </c>
-      <c r="O12" t="n">
+      <c r="V12" t="n">
         <v>86.81</v>
       </c>
-      <c r="P12" t="n">
+      <c r="W12" t="n">
         <v>79.38</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="X12" t="n">
         <v>83.51000000000001</v>
       </c>
-      <c r="R12" t="n">
+      <c r="Y12" t="n">
         <v>86.93000000000001</v>
       </c>
-      <c r="S12" t="n">
+      <c r="Z12" t="n">
         <v>91.73999999999999</v>
       </c>
-      <c r="T12" t="n">
-        <v>1.482</v>
-      </c>
-      <c r="U12" t="n">
+      <c r="AA12" t="n">
         <v>18482</v>
       </c>
     </row>
@@ -1317,6 +1603,9 @@
           <t>exp_123</t>
         </is>
       </c>
+      <c r="E13" t="n">
+        <v>100</v>
+      </c>
       <c r="F13" t="n">
         <v>1425472</v>
       </c>
@@ -1324,45 +1613,63 @@
         <v>36887</v>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="I13" t="n">
-        <v>1.4</v>
+        <v>0.755</v>
       </c>
       <c r="J13" t="n">
-        <v>0.755</v>
+        <v>14.95</v>
       </c>
       <c r="K13" t="n">
+        <v>82.53</v>
+      </c>
+      <c r="L13" t="n">
+        <v>89.68000000000001</v>
+      </c>
+      <c r="M13" t="n">
         <v>85.95999999999999</v>
       </c>
-      <c r="L13" t="n">
-        <v>82.53</v>
-      </c>
-      <c r="M13" t="n">
-        <v>89.68000000000001</v>
-      </c>
       <c r="N13" t="n">
+        <v>99.40000000000001</v>
+      </c>
+      <c r="O13" t="n">
+        <v>94.93000000000001</v>
+      </c>
+      <c r="P13" t="n">
+        <v>97.11</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>99.75</v>
+      </c>
+      <c r="R13" t="n">
+        <v>99.7</v>
+      </c>
+      <c r="S13" t="n">
+        <v>99.72</v>
+      </c>
+      <c r="T13" t="n">
+        <v>13.77</v>
+      </c>
+      <c r="U13" t="n">
         <v>84.42</v>
       </c>
-      <c r="O13" t="n">
+      <c r="V13" t="n">
         <v>87.54000000000001</v>
       </c>
-      <c r="P13" t="n">
+      <c r="W13" t="n">
         <v>80.45</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="X13" t="n">
         <v>84.58</v>
       </c>
-      <c r="R13" t="n">
+      <c r="Y13" t="n">
         <v>87.34</v>
       </c>
-      <c r="S13" t="n">
+      <c r="Z13" t="n">
         <v>92.03</v>
       </c>
-      <c r="T13" t="n">
-        <v>1.495</v>
-      </c>
-      <c r="U13" t="n">
+      <c r="AA13" t="n">
         <v>18934</v>
       </c>
     </row>
@@ -1385,6 +1692,9 @@
           <t>exp_112</t>
         </is>
       </c>
+      <c r="E14" t="n">
+        <v>100</v>
+      </c>
       <c r="F14" t="n">
         <v>209905</v>
       </c>
@@ -1392,45 +1702,63 @@
         <v>72594</v>
       </c>
       <c r="H14" t="n">
-        <v>0.25</v>
+        <v>2.165</v>
       </c>
       <c r="I14" t="n">
-        <v>2.165</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>0.9360000000000001</v>
+        <v>19.14</v>
       </c>
       <c r="K14" t="n">
+        <v>74.37</v>
+      </c>
+      <c r="L14" t="n">
+        <v>95.06</v>
+      </c>
+      <c r="M14" t="n">
         <v>83.45</v>
       </c>
-      <c r="L14" t="n">
-        <v>74.37</v>
-      </c>
-      <c r="M14" t="n">
-        <v>95.06</v>
-      </c>
       <c r="N14" t="n">
+        <v>99.81999999999999</v>
+      </c>
+      <c r="O14" t="n">
+        <v>99.56999999999999</v>
+      </c>
+      <c r="P14" t="n">
+        <v>99.69</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>99.91</v>
+      </c>
+      <c r="R14" t="n">
+        <v>100</v>
+      </c>
+      <c r="S14" t="n">
+        <v>99.95999999999999</v>
+      </c>
+      <c r="T14" t="n">
+        <v>16.51</v>
+      </c>
+      <c r="U14" t="n">
         <v>82.08</v>
       </c>
-      <c r="O14" t="n">
+      <c r="V14" t="n">
         <v>84.77</v>
       </c>
-      <c r="P14" t="n">
+      <c r="W14" t="n">
         <v>72.40000000000001</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="X14" t="n">
         <v>76.31</v>
       </c>
-      <c r="R14" t="n">
+      <c r="Y14" t="n">
         <v>93.55</v>
       </c>
-      <c r="S14" t="n">
+      <c r="Z14" t="n">
         <v>96.43000000000001</v>
       </c>
-      <c r="T14" t="n">
-        <v>1.914</v>
-      </c>
-      <c r="U14" t="n">
+      <c r="AA14" t="n">
         <v>40947</v>
       </c>
     </row>
@@ -1453,6 +1781,9 @@
           <t>exp_113</t>
         </is>
       </c>
+      <c r="E15" t="n">
+        <v>100</v>
+      </c>
       <c r="F15" t="n">
         <v>554000</v>
       </c>
@@ -1460,45 +1791,63 @@
         <v>65601</v>
       </c>
       <c r="H15" t="n">
-        <v>0.5</v>
+        <v>1.896</v>
       </c>
       <c r="I15" t="n">
-        <v>1.896</v>
+        <v>0.825</v>
       </c>
       <c r="J15" t="n">
-        <v>0.825</v>
+        <v>17.26</v>
       </c>
       <c r="K15" t="n">
+        <v>72.98</v>
+      </c>
+      <c r="L15" t="n">
+        <v>99.56999999999999</v>
+      </c>
+      <c r="M15" t="n">
         <v>84.23</v>
       </c>
-      <c r="L15" t="n">
-        <v>72.98</v>
-      </c>
-      <c r="M15" t="n">
-        <v>99.56999999999999</v>
-      </c>
       <c r="N15" t="n">
+        <v>99.78</v>
+      </c>
+      <c r="O15" t="n">
+        <v>100</v>
+      </c>
+      <c r="P15" t="n">
+        <v>99.89</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>99.95999999999999</v>
+      </c>
+      <c r="R15" t="n">
+        <v>100</v>
+      </c>
+      <c r="S15" t="n">
+        <v>99.98</v>
+      </c>
+      <c r="T15" t="n">
+        <v>15.75</v>
+      </c>
+      <c r="U15" t="n">
         <v>82.76000000000001</v>
       </c>
-      <c r="O15" t="n">
+      <c r="V15" t="n">
         <v>85.64</v>
       </c>
-      <c r="P15" t="n">
+      <c r="W15" t="n">
         <v>70.78</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="X15" t="n">
         <v>75.18000000000001</v>
       </c>
-      <c r="R15" t="n">
+      <c r="Y15" t="n">
         <v>99.23999999999999</v>
       </c>
-      <c r="S15" t="n">
+      <c r="Z15" t="n">
         <v>99.83</v>
       </c>
-      <c r="T15" t="n">
-        <v>1.726</v>
-      </c>
-      <c r="U15" t="n">
+      <c r="AA15" t="n">
         <v>34804</v>
       </c>
     </row>
@@ -1521,6 +1870,9 @@
           <t>exp_114</t>
         </is>
       </c>
+      <c r="E16" t="n">
+        <v>100</v>
+      </c>
       <c r="F16" t="n">
         <v>659404</v>
       </c>
@@ -1528,45 +1880,63 @@
         <v>76996</v>
       </c>
       <c r="H16" t="n">
-        <v>0.75</v>
+        <v>1.879</v>
       </c>
       <c r="I16" t="n">
-        <v>1.879</v>
+        <v>0.792</v>
       </c>
       <c r="J16" t="n">
-        <v>0.792</v>
+        <v>17.48</v>
       </c>
       <c r="K16" t="n">
+        <v>75.54000000000001</v>
+      </c>
+      <c r="L16" t="n">
+        <v>99.61</v>
+      </c>
+      <c r="M16" t="n">
         <v>85.92</v>
       </c>
-      <c r="L16" t="n">
-        <v>75.54000000000001</v>
-      </c>
-      <c r="M16" t="n">
-        <v>99.61</v>
-      </c>
       <c r="N16" t="n">
+        <v>99.95</v>
+      </c>
+      <c r="O16" t="n">
+        <v>100</v>
+      </c>
+      <c r="P16" t="n">
+        <v>99.97</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>99.98999999999999</v>
+      </c>
+      <c r="R16" t="n">
+        <v>100</v>
+      </c>
+      <c r="S16" t="n">
+        <v>99.98999999999999</v>
+      </c>
+      <c r="T16" t="n">
+        <v>14.07</v>
+      </c>
+      <c r="U16" t="n">
         <v>84.62</v>
       </c>
-      <c r="O16" t="n">
+      <c r="V16" t="n">
         <v>87.20999999999999</v>
       </c>
-      <c r="P16" t="n">
+      <c r="W16" t="n">
         <v>73.56</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="X16" t="n">
         <v>77.53</v>
       </c>
-      <c r="R16" t="n">
+      <c r="Y16" t="n">
         <v>99.33</v>
       </c>
-      <c r="S16" t="n">
+      <c r="Z16" t="n">
         <v>99.83</v>
       </c>
-      <c r="T16" t="n">
-        <v>1.748</v>
-      </c>
-      <c r="U16" t="n">
+      <c r="AA16" t="n">
         <v>41704</v>
       </c>
     </row>
@@ -1589,6 +1959,9 @@
           <t>exp_124</t>
         </is>
       </c>
+      <c r="E17" t="n">
+        <v>100</v>
+      </c>
       <c r="F17" t="n">
         <v>531040</v>
       </c>
@@ -1596,45 +1969,63 @@
         <v>89785</v>
       </c>
       <c r="H17" t="n">
-        <v>1</v>
+        <v>1.976</v>
       </c>
       <c r="I17" t="n">
-        <v>1.976</v>
+        <v>0.661</v>
       </c>
       <c r="J17" t="n">
-        <v>0.661</v>
+        <v>17.69</v>
       </c>
       <c r="K17" t="n">
+        <v>72.62</v>
+      </c>
+      <c r="L17" t="n">
+        <v>99.7</v>
+      </c>
+      <c r="M17" t="n">
         <v>84.03</v>
       </c>
-      <c r="L17" t="n">
-        <v>72.62</v>
-      </c>
-      <c r="M17" t="n">
-        <v>99.7</v>
-      </c>
       <c r="N17" t="n">
+        <v>99.88</v>
+      </c>
+      <c r="O17" t="n">
+        <v>100</v>
+      </c>
+      <c r="P17" t="n">
+        <v>99.94</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>99.98</v>
+      </c>
+      <c r="R17" t="n">
+        <v>100</v>
+      </c>
+      <c r="S17" t="n">
+        <v>99.98999999999999</v>
+      </c>
+      <c r="T17" t="n">
+        <v>15.95</v>
+      </c>
+      <c r="U17" t="n">
         <v>82.79000000000001</v>
       </c>
-      <c r="O17" t="n">
+      <c r="V17" t="n">
         <v>85.3</v>
       </c>
-      <c r="P17" t="n">
+      <c r="W17" t="n">
         <v>70.79000000000001</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="X17" t="n">
         <v>74.54000000000001</v>
       </c>
-      <c r="R17" t="n">
+      <c r="Y17" t="n">
         <v>99.40000000000001</v>
       </c>
-      <c r="S17" t="n">
+      <c r="Z17" t="n">
         <v>99.95999999999999</v>
       </c>
-      <c r="T17" t="n">
-        <v>1.769</v>
-      </c>
-      <c r="U17" t="n">
+      <c r="AA17" t="n">
         <v>51047</v>
       </c>
     </row>
@@ -1657,6 +2048,9 @@
           <t>exp_128</t>
         </is>
       </c>
+      <c r="E18" t="n">
+        <v>100</v>
+      </c>
       <c r="F18" t="n">
         <v>303609</v>
       </c>
@@ -1664,45 +2058,63 @@
         <v>81637</v>
       </c>
       <c r="H18" t="n">
-        <v>0.25</v>
+        <v>1.871</v>
       </c>
       <c r="I18" t="n">
-        <v>1.871</v>
+        <v>0.718</v>
       </c>
       <c r="J18" t="n">
-        <v>0.718</v>
+        <v>17.28</v>
       </c>
       <c r="K18" t="n">
+        <v>75.23999999999999</v>
+      </c>
+      <c r="L18" t="n">
+        <v>93.04000000000001</v>
+      </c>
+      <c r="M18" t="n">
         <v>83.19</v>
       </c>
-      <c r="L18" t="n">
-        <v>75.23999999999999</v>
-      </c>
-      <c r="M18" t="n">
-        <v>93.04000000000001</v>
-      </c>
       <c r="N18" t="n">
+        <v>99.48999999999999</v>
+      </c>
+      <c r="O18" t="n">
+        <v>97.94</v>
+      </c>
+      <c r="P18" t="n">
+        <v>98.70999999999999</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>99.68000000000001</v>
+      </c>
+      <c r="R18" t="n">
+        <v>99.79000000000001</v>
+      </c>
+      <c r="S18" t="n">
+        <v>99.73</v>
+      </c>
+      <c r="T18" t="n">
+        <v>16.54</v>
+      </c>
+      <c r="U18" t="n">
         <v>81.69</v>
       </c>
-      <c r="O18" t="n">
+      <c r="V18" t="n">
         <v>84.47</v>
       </c>
-      <c r="P18" t="n">
+      <c r="W18" t="n">
         <v>72.97</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="X18" t="n">
         <v>77.17</v>
       </c>
-      <c r="R18" t="n">
+      <c r="Y18" t="n">
         <v>91.2</v>
       </c>
-      <c r="S18" t="n">
+      <c r="Z18" t="n">
         <v>94.66</v>
       </c>
-      <c r="T18" t="n">
-        <v>1.728</v>
-      </c>
-      <c r="U18" t="n">
+      <c r="AA18" t="n">
         <v>48544</v>
       </c>
     </row>
@@ -1725,6 +2137,9 @@
           <t>exp_127</t>
         </is>
       </c>
+      <c r="E19" t="n">
+        <v>100</v>
+      </c>
       <c r="F19" t="n">
         <v>312179</v>
       </c>
@@ -1732,45 +2147,63 @@
         <v>98349</v>
       </c>
       <c r="H19" t="n">
-        <v>0.5</v>
+        <v>2.216</v>
       </c>
       <c r="I19" t="n">
-        <v>2.216</v>
+        <v>0.716</v>
       </c>
       <c r="J19" t="n">
-        <v>0.716</v>
+        <v>19.29</v>
       </c>
       <c r="K19" t="n">
+        <v>73.36</v>
+      </c>
+      <c r="L19" t="n">
+        <v>98.28</v>
+      </c>
+      <c r="M19" t="n">
         <v>84.01000000000001</v>
       </c>
-      <c r="L19" t="n">
-        <v>73.36</v>
-      </c>
-      <c r="M19" t="n">
-        <v>98.28</v>
-      </c>
       <c r="N19" t="n">
+        <v>99.84999999999999</v>
+      </c>
+      <c r="O19" t="n">
+        <v>99.18000000000001</v>
+      </c>
+      <c r="P19" t="n">
+        <v>99.52</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>99.97</v>
+      </c>
+      <c r="R19" t="n">
+        <v>100</v>
+      </c>
+      <c r="S19" t="n">
+        <v>99.98999999999999</v>
+      </c>
+      <c r="T19" t="n">
+        <v>15.98</v>
+      </c>
+      <c r="U19" t="n">
         <v>82.90000000000001</v>
       </c>
-      <c r="O19" t="n">
+      <c r="V19" t="n">
         <v>85.12</v>
       </c>
-      <c r="P19" t="n">
+      <c r="W19" t="n">
         <v>71.7</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="X19" t="n">
         <v>75.06999999999999</v>
       </c>
-      <c r="R19" t="n">
+      <c r="Y19" t="n">
         <v>97.44</v>
       </c>
-      <c r="S19" t="n">
+      <c r="Z19" t="n">
         <v>98.95999999999999</v>
       </c>
-      <c r="T19" t="n">
-        <v>1.929</v>
-      </c>
-      <c r="U19" t="n">
+      <c r="AA19" t="n">
         <v>57586</v>
       </c>
     </row>
@@ -1793,6 +2226,9 @@
           <t>exp_126</t>
         </is>
       </c>
+      <c r="E20" t="n">
+        <v>100</v>
+      </c>
       <c r="F20" t="n">
         <v>734656</v>
       </c>
@@ -1800,45 +2236,63 @@
         <v>70153</v>
       </c>
       <c r="H20" t="n">
-        <v>0.75</v>
+        <v>1.61</v>
       </c>
       <c r="I20" t="n">
-        <v>1.61</v>
+        <v>0.642</v>
       </c>
       <c r="J20" t="n">
-        <v>0.642</v>
+        <v>16.09</v>
       </c>
       <c r="K20" t="n">
+        <v>79.92</v>
+      </c>
+      <c r="L20" t="n">
+        <v>99.09999999999999</v>
+      </c>
+      <c r="M20" t="n">
         <v>88.48</v>
       </c>
-      <c r="L20" t="n">
-        <v>79.92</v>
-      </c>
-      <c r="M20" t="n">
-        <v>99.09999999999999</v>
-      </c>
       <c r="N20" t="n">
+        <v>99.95999999999999</v>
+      </c>
+      <c r="O20" t="n">
+        <v>99.95999999999999</v>
+      </c>
+      <c r="P20" t="n">
+        <v>99.95999999999999</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>99.98</v>
+      </c>
+      <c r="R20" t="n">
+        <v>100</v>
+      </c>
+      <c r="S20" t="n">
+        <v>99.98999999999999</v>
+      </c>
+      <c r="T20" t="n">
+        <v>11.51</v>
+      </c>
+      <c r="U20" t="n">
         <v>87.27</v>
       </c>
-      <c r="O20" t="n">
+      <c r="V20" t="n">
         <v>89.62</v>
       </c>
-      <c r="P20" t="n">
+      <c r="W20" t="n">
         <v>78.01000000000001</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="X20" t="n">
         <v>81.77</v>
       </c>
-      <c r="R20" t="n">
+      <c r="Y20" t="n">
         <v>98.56999999999999</v>
       </c>
-      <c r="S20" t="n">
+      <c r="Z20" t="n">
         <v>99.53</v>
       </c>
-      <c r="T20" t="n">
-        <v>1.609</v>
-      </c>
-      <c r="U20" t="n">
+      <c r="AA20" t="n">
         <v>33033</v>
       </c>
     </row>
@@ -1861,6 +2315,9 @@
           <t>exp_125</t>
         </is>
       </c>
+      <c r="E21" t="n">
+        <v>100</v>
+      </c>
       <c r="F21" t="n">
         <v>626966</v>
       </c>
@@ -1868,46 +2325,2297 @@
         <v>67190</v>
       </c>
       <c r="H21" t="n">
-        <v>1</v>
+        <v>1.706</v>
       </c>
       <c r="I21" t="n">
-        <v>1.706</v>
+        <v>0.577</v>
       </c>
       <c r="J21" t="n">
-        <v>0.577</v>
+        <v>16.44</v>
       </c>
       <c r="K21" t="n">
+        <v>75.92</v>
+      </c>
+      <c r="L21" t="n">
+        <v>98.5</v>
+      </c>
+      <c r="M21" t="n">
         <v>85.73999999999999</v>
       </c>
-      <c r="L21" t="n">
-        <v>75.92</v>
-      </c>
-      <c r="M21" t="n">
-        <v>98.5</v>
-      </c>
       <c r="N21" t="n">
+        <v>99.94</v>
+      </c>
+      <c r="O21" t="n">
+        <v>99.7</v>
+      </c>
+      <c r="P21" t="n">
+        <v>99.81999999999999</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>99.98999999999999</v>
+      </c>
+      <c r="R21" t="n">
+        <v>100</v>
+      </c>
+      <c r="S21" t="n">
+        <v>99.98999999999999</v>
+      </c>
+      <c r="T21" t="n">
+        <v>14.25</v>
+      </c>
+      <c r="U21" t="n">
         <v>84.41</v>
       </c>
-      <c r="O21" t="n">
+      <c r="V21" t="n">
         <v>87.04000000000001</v>
       </c>
-      <c r="P21" t="n">
+      <c r="W21" t="n">
         <v>73.87</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="X21" t="n">
         <v>77.95</v>
       </c>
-      <c r="R21" t="n">
+      <c r="Y21" t="n">
         <v>97.83</v>
       </c>
-      <c r="S21" t="n">
+      <c r="Z21" t="n">
         <v>99.09999999999999</v>
       </c>
-      <c r="T21" t="n">
-        <v>1.644</v>
-      </c>
-      <c r="U21" t="n">
+      <c r="AA21" t="n">
         <v>32773</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H63"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Paired block-bootstrap difference between frame counts, 2000 draws, 5 cm blocks. CI spanning 0 = not resolvable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>method</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t>pair</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="inlineStr">
+        <is>
+          <t>Δ@3cm (pp)</t>
+        </is>
+      </c>
+      <c r="F3" s="1" t="inlineStr">
+        <is>
+          <t>95% CI lo</t>
+        </is>
+      </c>
+      <c r="G3" s="1" t="inlineStr">
+        <is>
+          <t>95% CI hi</t>
+        </is>
+      </c>
+      <c r="H3" s="1" t="inlineStr">
+        <is>
+          <t>resolvable?</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>information_sign_002</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>COLMAP</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>N=50 - N=25</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>11.03</v>
+      </c>
+      <c r="F4" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="G4" t="n">
+        <v>13.78</v>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>information_sign_002</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>COLMAP</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>accuracy</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>N=50 - N=25</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>5.92</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="G5" t="n">
+        <v>9.609999999999999</v>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>information_sign_002</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>COLMAP</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>N=75 - N=25</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>11.38</v>
+      </c>
+      <c r="F6" t="n">
+        <v>8.640000000000001</v>
+      </c>
+      <c r="G6" t="n">
+        <v>14.06</v>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>information_sign_002</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>COLMAP</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>accuracy</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>N=75 - N=25</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>7.33</v>
+      </c>
+      <c r="F7" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="G7" t="n">
+        <v>10.83</v>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>information_sign_002</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>COLMAP</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>N=100 - N=25</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>12.07</v>
+      </c>
+      <c r="F8" t="n">
+        <v>9.369999999999999</v>
+      </c>
+      <c r="G8" t="n">
+        <v>14.82</v>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>information_sign_002</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>COLMAP</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>accuracy</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>N=100 - N=25</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="F9" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="G9" t="n">
+        <v>12.03</v>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>information_sign_002</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>COLMAP</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>N=75 - N=50</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-1.87</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>no - CI spans 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>information_sign_002</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>COLMAP</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>accuracy</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>N=75 - N=50</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-1.59</v>
+      </c>
+      <c r="G11" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>no - CI spans 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>information_sign_002</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>COLMAP</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>N=100 - N=50</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-1.05</v>
+      </c>
+      <c r="G12" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>no - CI spans 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>information_sign_002</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>COLMAP</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>accuracy</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>N=100 - N=50</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-0.37</v>
+      </c>
+      <c r="G13" t="n">
+        <v>5.69</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>no - CI spans 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>information_sign_002</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>COLMAP</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>N=100 - N=75</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-1.37</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>no - CI spans 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>information_sign_002</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>COLMAP</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>accuracy</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>N=100 - N=75</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-1.87</v>
+      </c>
+      <c r="G15" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>no - CI spans 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>information_sign_002</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>MASt3R-GA</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>N=50 - N=25</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="G16" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>no - CI spans 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>information_sign_002</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>MASt3R-GA</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>accuracy</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>N=50 - N=25</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>-1.43</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-4.27</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>no - CI spans 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>information_sign_002</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>MASt3R-GA</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>N=75 - N=25</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="G18" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>information_sign_002</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>MASt3R-GA</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>accuracy</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>N=75 - N=25</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-1.65</v>
+      </c>
+      <c r="G19" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>no - CI spans 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>information_sign_002</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>MASt3R-GA</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>N=100 - N=25</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F20" t="n">
+        <v>-1.24</v>
+      </c>
+      <c r="G20" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>no - CI spans 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>information_sign_002</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>MASt3R-GA</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>accuracy</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>N=100 - N=25</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>-1.72</v>
+      </c>
+      <c r="F21" t="n">
+        <v>-4.33</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>no - CI spans 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>information_sign_002</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>MASt3R-GA</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>N=75 - N=50</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="F22" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="G22" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>no - CI spans 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>information_sign_002</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>MASt3R-GA</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>accuracy</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>N=75 - N=50</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="G23" t="n">
+        <v>5.47</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>no - CI spans 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>information_sign_002</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>MASt3R-GA</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>N=100 - N=50</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-2.13</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>no - CI spans 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>information_sign_002</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>MASt3R-GA</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>accuracy</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>N=100 - N=50</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-3.25</v>
+      </c>
+      <c r="G25" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>no - CI spans 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>information_sign_002</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>MASt3R-GA</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>N=100 - N=75</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>-1.85</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-3.73</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>information_sign_002</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>MASt3R-GA</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>accuracy</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>N=100 - N=75</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>-2.86</v>
+      </c>
+      <c r="F27" t="n">
+        <v>-5.66</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>information_sign_002</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>MASt3R-GA (logwin-7)</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>N=50 - N=25</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="F28" t="n">
+        <v>-0.97</v>
+      </c>
+      <c r="G28" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>no - CI spans 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>information_sign_002</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>MASt3R-GA (logwin-7)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>accuracy</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>N=50 - N=25</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>-1.85</v>
+      </c>
+      <c r="F29" t="n">
+        <v>-4.49</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>no - CI spans 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>information_sign_002</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>MASt3R-GA (logwin-7)</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>N=75 - N=25</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>5.31</v>
+      </c>
+      <c r="F30" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="G30" t="n">
+        <v>7.18</v>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>information_sign_002</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>MASt3R-GA (logwin-7)</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>accuracy</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>N=75 - N=25</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="F31" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="G31" t="n">
+        <v>7.51</v>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>information_sign_002</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>MASt3R-GA (logwin-7)</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>N=100 - N=25</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="G32" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>information_sign_002</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>MASt3R-GA (logwin-7)</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>accuracy</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>N=100 - N=25</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="F33" t="n">
+        <v>-2.19</v>
+      </c>
+      <c r="G33" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>no - CI spans 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>information_sign_002</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>MASt3R-GA (logwin-7)</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>N=75 - N=50</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>4.47</v>
+      </c>
+      <c r="F34" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="G34" t="n">
+        <v>6.04</v>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>information_sign_002</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>MASt3R-GA (logwin-7)</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>accuracy</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>N=75 - N=50</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6.56</v>
+      </c>
+      <c r="F35" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="G35" t="n">
+        <v>8.960000000000001</v>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>information_sign_002</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>MASt3R-GA (logwin-7)</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>N=100 - N=50</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G36" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>information_sign_002</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>MASt3R-GA (logwin-7)</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>accuracy</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>N=100 - N=50</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="F37" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="G37" t="n">
+        <v>5.06</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>no - CI spans 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>information_sign_002</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>MASt3R-GA (logwin-7)</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>N=100 - N=75</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>-2.76</v>
+      </c>
+      <c r="F38" t="n">
+        <v>-4.52</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-1.03</v>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>information_sign_002</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>MASt3R-GA (logwin-7)</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>accuracy</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>N=100 - N=75</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>-4.04</v>
+      </c>
+      <c r="F39" t="n">
+        <v>-6.77</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-1.28</v>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>bollard_003</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>COLMAP</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>N=30 - N=15</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>38.66</v>
+      </c>
+      <c r="F40" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="G40" t="n">
+        <v>45.56</v>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>bollard_003</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>COLMAP</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>accuracy</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>N=30 - N=15</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="F41" t="n">
+        <v>-2.68</v>
+      </c>
+      <c r="G41" t="n">
+        <v>8.77</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>no - CI spans 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>bollard_003</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>COLMAP</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>N=45 - N=15</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>41.86</v>
+      </c>
+      <c r="F42" t="n">
+        <v>35.08</v>
+      </c>
+      <c r="G42" t="n">
+        <v>48.43</v>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>bollard_003</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>COLMAP</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>accuracy</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>N=45 - N=15</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="F43" t="n">
+        <v>-4.06</v>
+      </c>
+      <c r="G43" t="n">
+        <v>7.17</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>no - CI spans 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>bollard_003</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>COLMAP</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>N=60 - N=15</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>47.56</v>
+      </c>
+      <c r="F44" t="n">
+        <v>40.89</v>
+      </c>
+      <c r="G44" t="n">
+        <v>53.93</v>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>bollard_003</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>COLMAP</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>accuracy</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>N=60 - N=15</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F45" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="G45" t="n">
+        <v>10.22</v>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>no - CI spans 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>bollard_003</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>COLMAP</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>N=45 - N=30</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="F46" t="n">
+        <v>-0.8100000000000001</v>
+      </c>
+      <c r="G46" t="n">
+        <v>7.49</v>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>no - CI spans 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>bollard_003</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>COLMAP</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>accuracy</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>N=45 - N=30</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>-1.58</v>
+      </c>
+      <c r="F47" t="n">
+        <v>-6.27</v>
+      </c>
+      <c r="G47" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>no - CI spans 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>bollard_003</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>COLMAP</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>N=60 - N=30</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="F48" t="n">
+        <v>5.17</v>
+      </c>
+      <c r="G48" t="n">
+        <v>12.75</v>
+      </c>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>bollard_003</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>COLMAP</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>accuracy</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>N=60 - N=30</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="F49" t="n">
+        <v>-2.32</v>
+      </c>
+      <c r="G49" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>no - CI spans 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>bollard_003</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>COLMAP</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>N=60 - N=45</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="F50" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="G50" t="n">
+        <v>9</v>
+      </c>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>bollard_003</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>COLMAP</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>accuracy</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>N=60 - N=45</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="F51" t="n">
+        <v>-0.82</v>
+      </c>
+      <c r="G51" t="n">
+        <v>7.19</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>no - CI spans 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>bollard_003</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>MASt3R-GA</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>N=30 - N=15</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="F52" t="n">
+        <v>-1.49</v>
+      </c>
+      <c r="G52" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>no - CI spans 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>bollard_003</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>MASt3R-GA</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>accuracy</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>N=30 - N=15</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="F53" t="n">
+        <v>-2.93</v>
+      </c>
+      <c r="G53" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>no - CI spans 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>bollard_003</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>MASt3R-GA</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>N=45 - N=15</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="F54" t="n">
+        <v>-1.17</v>
+      </c>
+      <c r="G54" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>no - CI spans 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>bollard_003</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>MASt3R-GA</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>accuracy</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>N=45 - N=15</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="F55" t="n">
+        <v>-2.78</v>
+      </c>
+      <c r="G55" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>no - CI spans 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>bollard_003</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>MASt3R-GA</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>N=60 - N=15</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="F56" t="n">
+        <v>-1.93</v>
+      </c>
+      <c r="G56" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>no - CI spans 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>bollard_003</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>MASt3R-GA</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>accuracy</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>N=60 - N=15</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="F57" t="n">
+        <v>-3.14</v>
+      </c>
+      <c r="G57" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>no - CI spans 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>bollard_003</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>MASt3R-GA</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>N=45 - N=30</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="F58" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="G58" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>no - CI spans 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>bollard_003</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>MASt3R-GA</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>accuracy</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>N=45 - N=30</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="F59" t="n">
+        <v>-3.14</v>
+      </c>
+      <c r="G59" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>no - CI spans 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>bollard_003</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>MASt3R-GA</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>N=60 - N=30</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="F60" t="n">
+        <v>-2.32</v>
+      </c>
+      <c r="G60" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>no - CI spans 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>bollard_003</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>MASt3R-GA</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>accuracy</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>N=60 - N=30</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="F61" t="n">
+        <v>-3.54</v>
+      </c>
+      <c r="G61" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>no - CI spans 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>bollard_003</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>MASt3R-GA</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>N=60 - N=45</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>-0.77</v>
+      </c>
+      <c r="F62" t="n">
+        <v>-2.61</v>
+      </c>
+      <c r="G62" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>no - CI spans 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>bollard_003</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>MASt3R-GA</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>accuracy</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>N=60 - N=45</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>-0.26</v>
+      </c>
+      <c r="F63" t="n">
+        <v>-3.36</v>
+      </c>
+      <c r="G63" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>no - CI spans 0</t>
+        </is>
       </c>
     </row>
   </sheetData>
